--- a/docentes/Castillo Cruz Carlos Samuel - Estadisticos 20241.xlsx
+++ b/docentes/Castillo Cruz Carlos Samuel - Estadisticos 20241.xlsx
@@ -530,16 +530,19 @@
         <v>25</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>25</v>
       </c>
-      <c r="E2">
-        <v>25</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -604,7 +607,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Castillo Cruz Carlos Samuel - Estadisticos 20241.xlsx
+++ b/docentes/Castillo Cruz Carlos Samuel - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -65,6 +65,42 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>PARRA</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>EFRAIN DE JESUS</t>
+  </si>
+  <si>
+    <t>GAMALIEL</t>
+  </si>
+  <si>
+    <t>MOISES ALBERTO</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
   </si>
 </sst>
 </file>
@@ -462,10 +498,10 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -474,7 +510,7 @@
         <v>25</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H2">
         <v>9.199999999999999</v>
@@ -527,10 +563,10 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -539,7 +575,7 @@
         <v>25</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H2">
         <v>9.199999999999999</v>
@@ -592,10 +628,10 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -604,7 +640,7 @@
         <v>25</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H2">
         <v>9.4</v>
@@ -617,7 +653,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -647,6 +683,98 @@
         <v>15</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>22330051920291</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920305</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330051920309</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920315</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Castillo Cruz Carlos Samuel - Estadisticos 20241.xlsx
+++ b/docentes/Castillo Cruz Carlos Samuel - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
   <si>
     <t>Mat</t>
   </si>
@@ -65,42 +65,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>EFRAIN DE JESUS</t>
-  </si>
-  <si>
-    <t>GAMALIEL</t>
-  </si>
-  <si>
-    <t>MOISES ALBERTO</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
   </si>
 </sst>
 </file>
@@ -501,19 +465,19 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>86.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -566,19 +530,19 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>86.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -631,19 +595,19 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>86.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>
@@ -653,7 +617,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -683,98 +647,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920291</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920305</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920309</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920315</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
